--- a/docs/sample-output/fs-feasibility-sample-waller-garden-apartments.xlsx
+++ b/docs/sample-output/fs-feasibility-sample-waller-garden-apartments.xlsx
@@ -49,7 +49,7 @@
     <t>Inputs hash</t>
   </si>
   <si>
-    <t>332a5c7a</t>
+    <t>74b2c4fe</t>
   </si>
   <si>
     <t>Scope</t>
@@ -1186,7 +1186,7 @@
     <t>Share of contract</t>
   </si>
   <si>
-    <t>Profit — GC fee on library lines (12%)</t>
+    <t>Profit — GC fee on library lines</t>
   </si>
   <si>
     <t>Construction contingency</t>
@@ -10205,31 +10205,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="9">
-        <v>4368347</v>
+        <v>3997655.5200000005</v>
       </c>
       <c r="C2" s="9">
         <v>3175045.8624067</v>
       </c>
       <c r="D2" s="9">
-        <v>1193301.1375933</v>
+        <v>822609.6575933006</v>
       </c>
       <c r="E2" s="8">
-        <v>1.3758374490656247</v>
+        <v>1.2590859134770918</v>
       </c>
       <c r="F2" s="16">
-        <v>0.030853959753777492</v>
+        <v>0.021269371551628093</v>
       </c>
       <c r="G2" s="9">
-        <v>78250000</v>
+        <v>71610000</v>
       </c>
       <c r="H2" s="9">
-        <v>36163418.95489147</v>
+        <v>29656218.954891473</v>
       </c>
       <c r="I2" s="16">
-        <v>-0.03410572406646749</v>
+        <v>-0.21194028755559455</v>
       </c>
       <c r="J2" s="16">
-        <v>0.023043710700732203</v>
+        <v>-0.06376804824476791</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -10237,31 +10237,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="9">
-        <v>4499397.41</v>
+        <v>4117585.1856</v>
       </c>
       <c r="C3" s="9">
         <v>3175045.8624067</v>
       </c>
       <c r="D3" s="9">
-        <v>1324351.5475933002</v>
+        <v>942539.3231933</v>
       </c>
       <c r="E3" s="8">
-        <v>1.4171125725375933</v>
+        <v>1.2968584908814045</v>
       </c>
       <c r="F3" s="16">
-        <v>0.03424239537029839</v>
+        <v>0.024370269522084494</v>
       </c>
       <c r="G3" s="9">
-        <v>80598000</v>
+        <v>73758000</v>
       </c>
       <c r="H3" s="9">
-        <v>38934796.83430326</v>
+        <v>32231596.83430326</v>
       </c>
       <c r="I3" s="16">
-        <v>0.035807972289757496</v>
+        <v>-0.06315658880875864</v>
       </c>
       <c r="J3" s="16">
-        <v>0.054457422210139446</v>
+        <v>0.0075484667644218646</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -10269,31 +10269,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="9">
-        <v>4634379.3323</v>
+        <v>4241112.741168</v>
       </c>
       <c r="C4" s="9">
         <v>3175045.8624067</v>
       </c>
       <c r="D4" s="9">
-        <v>1459333.4698933</v>
+        <v>1066066.8787613</v>
       </c>
       <c r="E4" s="8">
-        <v>1.4596259497137212</v>
+        <v>1.3357642456078465</v>
       </c>
       <c r="F4" s="16">
-        <v>0.03773248405531491</v>
+        <v>0.027564194431654594</v>
       </c>
       <c r="G4" s="9">
-        <v>83016000</v>
+        <v>75971000</v>
       </c>
       <c r="H4" s="9">
-        <v>41807323.297226414</v>
+        <v>34903223.297226414</v>
       </c>
       <c r="I4" s="16">
-        <v>0.05958709879625072</v>
+        <v>-0.008369151548194287</v>
       </c>
       <c r="J4" s="16">
-        <v>0.06513133829831262</v>
+        <v>0.03249879287971646</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -10301,31 +10301,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="9">
-        <v>4773410.712269</v>
+        <v>4368346.123403041</v>
       </c>
       <c r="C5" s="9">
         <v>3175045.8624067</v>
       </c>
       <c r="D5" s="9">
-        <v>1598364.8498622999</v>
+        <v>1193300.2609963408</v>
       </c>
       <c r="E5" s="8">
-        <v>1.5034147282051327</v>
+        <v>1.375837172976082</v>
       </c>
       <c r="F5" s="16">
-        <v>0.04132727540088192</v>
+        <v>0.030853937088511824</v>
       </c>
       <c r="G5" s="9">
-        <v>85506000</v>
+        <v>78250000</v>
       </c>
       <c r="H5" s="9">
-        <v>44785210.78883912</v>
+        <v>37674330.78883912</v>
       </c>
       <c r="I5" s="16">
-        <v>0.07125152534919071</v>
+        <v>0.019651067816708282</v>
       </c>
       <c r="J5" s="16">
-        <v>0.07049986711034592</v>
+        <v>0.04518868442671843</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -10333,31 +10333,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="9">
-        <v>4916613.03363707</v>
+        <v>4499396.507105131</v>
       </c>
       <c r="C6" s="9">
         <v>3175045.8624067</v>
       </c>
       <c r="D6" s="9">
-        <v>1741567.1712303702</v>
+        <v>1324350.6446984308</v>
       </c>
       <c r="E6" s="8">
-        <v>1.5485171700512868</v>
+        <v>1.4171122881653642</v>
       </c>
       <c r="F6" s="16">
-        <v>0.045029910486815955</v>
+        <v>0.03424237202507472</v>
       </c>
       <c r="G6" s="9">
-        <v>88072000</v>
+        <v>80598000</v>
       </c>
       <c r="H6" s="9">
-        <v>47874787.62928347</v>
+        <v>40550267.62928347</v>
       </c>
       <c r="I6" s="16">
-        <v>0.07801060922637303</v>
+        <v>0.036440227391887486</v>
       </c>
       <c r="J6" s="16">
-        <v>0.07373064658445179</v>
+        <v>0.05286592465203893</v>
       </c>
     </row>
   </sheetData>
@@ -10417,16 +10417,16 @@
         <v>413</v>
       </c>
       <c r="B3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C3" s="16">
+        <v>0.00006133263068508477</v>
+      </c>
+      <c r="D3" t="s">
         <v>411</v>
       </c>
-      <c r="C3" s="16">
-        <v>0.06890622270240732</v>
-      </c>
-      <c r="D3" t="s">
-        <v>412</v>
-      </c>
       <c r="E3" s="16">
-        <v>0.004721407485094531</v>
+        <v>0.07497481696117236</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -10548,19 +10548,19 @@
         <v>433</v>
       </c>
       <c r="B12" s="16">
-        <v>0.010817556569622466</v>
+        <v>0.016436027552555244</v>
       </c>
       <c r="C12" s="16">
-        <v>0.040485130711992</v>
+        <v>0.04632424403972091</v>
       </c>
       <c r="D12" s="16">
-        <v>0.06890622270240732</v>
+        <v>0.07497481696117236</v>
       </c>
       <c r="E12" s="16">
-        <v>0.09625035238192625</v>
+        <v>0.10255345309501096</v>
       </c>
       <c r="F12" s="16">
-        <v>0.12264270404225375</v>
+        <v>0.12918234754495317</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -10568,19 +10568,19 @@
         <v>434</v>
       </c>
       <c r="B13" s="16">
-        <v>-0.0056603894520577125</v>
+        <v>-0.0030365239258988153</v>
       </c>
       <c r="C13" s="16">
-        <v>0.023543060554188866</v>
+        <v>0.026264710338840702</v>
       </c>
       <c r="D13" s="16">
-        <v>0.05149478991679457</v>
+        <v>0.0543194668912399</v>
       </c>
       <c r="E13" s="16">
-        <v>0.0783748043574346</v>
+        <v>0.08130587742328221</v>
       </c>
       <c r="F13" s="16">
-        <v>0.10431597961329842</v>
+        <v>0.10735534782241252</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -10608,19 +10608,19 @@
         <v>436</v>
       </c>
       <c r="B15" s="16">
-        <v>-0.03601962296269412</v>
+        <v>-0.03833733142351259</v>
       </c>
       <c r="C15" s="16">
-        <v>-0.0076256919856867444</v>
+        <v>-0.010019173091904143</v>
       </c>
       <c r="D15" s="16">
-        <v>0.01948696614432399</v>
+        <v>0.01701128602092572</v>
       </c>
       <c r="E15" s="16">
-        <v>0.04551992748304401</v>
+        <v>0.042957459429219025</v>
       </c>
       <c r="F15" s="16">
-        <v>0.07062216993377568</v>
+        <v>0.06796974220280982</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -10628,19 +10628,19 @@
         <v>437</v>
       </c>
       <c r="B16" s="16">
-        <v>-0.0500689678121049</v>
+        <v>-0.05445069356556498</v>
       </c>
       <c r="C16" s="16">
-        <v>-0.02202187172827408</v>
+        <v>-0.026535904459511483</v>
       </c>
       <c r="D16" s="16">
-        <v>0.004721407485094531</v>
+        <v>0.00006133263068508477</v>
       </c>
       <c r="E16" s="16">
-        <v>0.030373459643653344</v>
+        <v>0.02555729023345865</v>
       </c>
       <c r="F16" s="16">
-        <v>0.0550915032549788</v>
+        <v>0.050111988188299206</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
